--- a/MedCare_Nigeria_Analytics.xlsx
+++ b/MedCare_Nigeria_Analytics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020DB5F7-C425-4D4B-9EAF-1AA9AE333AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25453D9-0132-48A4-B5A6-7BCF91338B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="hGF9N2NDggN+oMjnKUuIu5sFV5OAs4694ZSuLf48dtIRbsWARI195EPvHH+rizpfFhKyHUJkmJY+YO8Tt/1EHA==" workbookSaltValue="zPj7YAqIYX1+2q+Ta+ENqw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -2245,8 +2245,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="[$₦-469]\ #,##0"/>
-    <numFmt numFmtId="167" formatCode="[$₦-469]\ #,##0;\-[$₦-469]\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="[$₦-469]\ #,##0"/>
+    <numFmt numFmtId="166" formatCode="[$₦-469]\ #,##0;\-[$₦-469]\ #,##0"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -2387,15 +2387,15 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2430,6 +2430,11 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Hospital Name</v>
+          </cell>
+        </row>
         <row r="2">
           <cell r="A2" t="str">
             <v>Palmgrove Specialist Hospital</v>
@@ -2659,15 +2664,7 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Hospital Name</v>
-          </cell>
-        </row>
         <row r="2">
-          <cell r="A2" t="str">
-            <v>Palmgrove Specialist Hospital</v>
-          </cell>
           <cell r="B2" t="str">
             <v>MC-LAG-01</v>
           </cell>
@@ -2679,9 +2676,6 @@
           </cell>
         </row>
         <row r="3">
-          <cell r="A3" t="str">
-            <v>Brightwell Medical Centre</v>
-          </cell>
           <cell r="B3" t="str">
             <v>MC-LAG-02</v>
           </cell>
@@ -2693,9 +2687,6 @@
           </cell>
         </row>
         <row r="4">
-          <cell r="A4" t="str">
-            <v>Lakeview Road General Hospital</v>
-          </cell>
           <cell r="B4" t="str">
             <v>MC-LAG-03</v>
           </cell>
@@ -2707,9 +2698,6 @@
           </cell>
         </row>
         <row r="5">
-          <cell r="A5" t="str">
-            <v>Kingsgate Specialist Hospital</v>
-          </cell>
           <cell r="B5" t="str">
             <v>MC-ABJ-01</v>
           </cell>
@@ -2721,9 +2709,6 @@
           </cell>
         </row>
         <row r="6">
-          <cell r="A6" t="str">
-            <v>Silverbell Medical Centre</v>
-          </cell>
           <cell r="B6" t="str">
             <v>MC-ABJ-02</v>
           </cell>
@@ -2735,9 +2720,6 @@
           </cell>
         </row>
         <row r="7">
-          <cell r="A7" t="str">
-            <v>Northview General Hospital</v>
-          </cell>
           <cell r="B7" t="str">
             <v>MC-ABJ-03</v>
           </cell>
@@ -2749,9 +2731,6 @@
           </cell>
         </row>
         <row r="8">
-          <cell r="A8" t="str">
-            <v>Savannah Specialist Hospital</v>
-          </cell>
           <cell r="B8" t="str">
             <v>MC-KAN-01</v>
           </cell>
@@ -2763,9 +2742,6 @@
           </cell>
         </row>
         <row r="9">
-          <cell r="A9" t="str">
-            <v>Goldcrest Medical Centre</v>
-          </cell>
           <cell r="B9" t="str">
             <v>MC-KAN-02</v>
           </cell>
@@ -2777,9 +2753,6 @@
           </cell>
         </row>
         <row r="10">
-          <cell r="A10" t="str">
-            <v>Riverbend General Hospital</v>
-          </cell>
           <cell r="B10" t="str">
             <v>MC-KAN-03</v>
           </cell>
@@ -2791,9 +2764,6 @@
           </cell>
         </row>
         <row r="11">
-          <cell r="A11" t="str">
-            <v>Harborlight Specialist Hospital</v>
-          </cell>
           <cell r="B11" t="str">
             <v>MC-PHC-01</v>
           </cell>
@@ -2805,9 +2775,6 @@
           </cell>
         </row>
         <row r="12">
-          <cell r="A12" t="str">
-            <v>Bluewater Medical Centre</v>
-          </cell>
           <cell r="B12" t="str">
             <v>MC-PHC-02</v>
           </cell>
@@ -2819,9 +2786,6 @@
           </cell>
         </row>
         <row r="13">
-          <cell r="A13" t="str">
-            <v>Palmfield General Hospital</v>
-          </cell>
           <cell r="B13" t="str">
             <v>MC-PHC-03</v>
           </cell>
@@ -2833,9 +2797,6 @@
           </cell>
         </row>
         <row r="14">
-          <cell r="A14" t="str">
-            <v>Hilltown Specialist Hospital</v>
-          </cell>
           <cell r="B14" t="str">
             <v>MC-ENU-01</v>
           </cell>
@@ -2847,9 +2808,6 @@
           </cell>
         </row>
         <row r="15">
-          <cell r="A15" t="str">
-            <v>Cedarview Medical Centre</v>
-          </cell>
           <cell r="B15" t="str">
             <v>MC-ENU-02</v>
           </cell>
@@ -2861,9 +2819,6 @@
           </cell>
         </row>
         <row r="16">
-          <cell r="A16" t="str">
-            <v>Greenridge General Hospital</v>
-          </cell>
           <cell r="B16" t="str">
             <v>MC-ENU-03</v>
           </cell>
@@ -3369,7 +3324,7 @@
         <v>Dr. Blessing Adekunle</v>
       </c>
       <c r="L2" t="str">
-        <f>VLOOKUP(TRIM(D2),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D2),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M2" t="str">
@@ -3385,7 +3340,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P2" t="str">
-        <f>VLOOKUP(TRIM(D2),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L2,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q2" t="str" cm="1">
@@ -3437,7 +3392,7 @@
         <v>Dr. Amaka Nwosu</v>
       </c>
       <c r="L3" t="str">
-        <f>VLOOKUP(TRIM(D3),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D3),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-01</v>
       </c>
       <c r="M3" t="str">
@@ -3453,7 +3408,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P3" t="str">
-        <f>VLOOKUP(TRIM(D3),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L3,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q3" t="str" cm="1">
@@ -3505,7 +3460,7 @@
         <v>Dr. Ronke Nnaji</v>
       </c>
       <c r="L4" t="str">
-        <f>VLOOKUP(TRIM(D4),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D4),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-03</v>
       </c>
       <c r="M4" t="str">
@@ -3521,7 +3476,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P4" t="str">
-        <f>VLOOKUP(TRIM(D4),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L4,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q4" t="str" cm="1">
@@ -3573,7 +3528,7 @@
         <v>Dr. Blessing Adekunle</v>
       </c>
       <c r="L5" t="str">
-        <f>VLOOKUP(TRIM(D5),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D5),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M5" t="str">
@@ -3589,7 +3544,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P5" t="str">
-        <f>VLOOKUP(TRIM(D5),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L5,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q5" t="str" cm="1">
@@ -3641,7 +3596,7 @@
         <v>Dr. Blessing Obi</v>
       </c>
       <c r="L6" t="str">
-        <f>VLOOKUP(TRIM(D6),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D6),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M6" t="str">
@@ -3657,7 +3612,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P6" t="str">
-        <f>VLOOKUP(TRIM(D6),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L6,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q6" t="str" cm="1">
@@ -3709,7 +3664,7 @@
         <v>Dr. Amaka Okafor</v>
       </c>
       <c r="L7" t="str">
-        <f>VLOOKUP(TRIM(D7),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D7),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M7" t="str">
@@ -3725,7 +3680,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P7" t="str">
-        <f>VLOOKUP(TRIM(D7),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L7,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q7" t="str" cm="1">
@@ -3777,7 +3732,7 @@
         <v>No name</v>
       </c>
       <c r="L8" t="str">
-        <f>VLOOKUP(TRIM(D8),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D8),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M8" t="str">
@@ -3793,7 +3748,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P8" t="str">
-        <f>VLOOKUP(TRIM(D8),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L8,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q8" t="str" cm="1">
@@ -3845,7 +3800,7 @@
         <v>Dr. Damilola Chidozie</v>
       </c>
       <c r="L9" t="str">
-        <f>VLOOKUP(TRIM(D9),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D9),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M9" t="str">
@@ -3861,7 +3816,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P9" t="str">
-        <f>VLOOKUP(TRIM(D9),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L9,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q9" t="str" cm="1">
@@ -3913,7 +3868,7 @@
         <v>Dr. Zainab Lawal</v>
       </c>
       <c r="L10" t="str">
-        <f>VLOOKUP(TRIM(D10),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D10),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M10" t="str">
@@ -3929,7 +3884,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P10" t="str">
-        <f>VLOOKUP(TRIM(D10),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L10,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q10" t="str" cm="1">
@@ -3981,7 +3936,7 @@
         <v>Dr. Yusuf Usman</v>
       </c>
       <c r="L11" t="str">
-        <f>VLOOKUP(TRIM(D11),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D11),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M11" t="str">
@@ -3997,7 +3952,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P11" t="str">
-        <f>VLOOKUP(TRIM(D11),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L11,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q11" t="str" cm="1">
@@ -4049,7 +4004,7 @@
         <v>Dr. Oluwaseun Okoye</v>
       </c>
       <c r="L12" t="str">
-        <f>VLOOKUP(TRIM(D12),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D12),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M12" t="str">
@@ -4065,7 +4020,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P12" t="str">
-        <f>VLOOKUP(TRIM(D12),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L12,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q12" t="str" cm="1">
@@ -4117,7 +4072,7 @@
         <v>Dr. Folake Bamidele</v>
       </c>
       <c r="L13" t="str">
-        <f>VLOOKUP(TRIM(D13),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D13),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-01</v>
       </c>
       <c r="M13" t="str">
@@ -4133,7 +4088,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P13" t="str">
-        <f>VLOOKUP(TRIM(D13),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L13,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q13" t="str" cm="1">
@@ -4185,7 +4140,7 @@
         <v>Dr. Oluwaseun Okoye</v>
       </c>
       <c r="L14" t="str">
-        <f>VLOOKUP(TRIM(D14),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D14),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M14" t="str">
@@ -4201,7 +4156,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P14" t="str">
-        <f>VLOOKUP(TRIM(D14),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L14,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q14" t="str" cm="1">
@@ -4253,7 +4208,7 @@
         <v>Dr. Blessing Obi</v>
       </c>
       <c r="L15" t="str">
-        <f>VLOOKUP(TRIM(D15),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D15),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-01</v>
       </c>
       <c r="M15" t="str">
@@ -4269,7 +4224,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P15" t="str">
-        <f>VLOOKUP(TRIM(D15),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L15,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q15" t="str" cm="1">
@@ -4321,7 +4276,7 @@
         <v>Dr. Ngozi Umar</v>
       </c>
       <c r="L16" t="str">
-        <f>VLOOKUP(TRIM(D16),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D16),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M16" t="str">
@@ -4337,7 +4292,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P16" t="str">
-        <f>VLOOKUP(TRIM(D16),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L16,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q16" t="str" cm="1">
@@ -4389,7 +4344,7 @@
         <v>Dr. Blessing Obi</v>
       </c>
       <c r="L17" t="str">
-        <f>VLOOKUP(TRIM(D17),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D17),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M17" t="str">
@@ -4405,7 +4360,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P17" t="str">
-        <f>VLOOKUP(TRIM(D17),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L17,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q17" t="str" cm="1">
@@ -4457,7 +4412,7 @@
         <v>Dr. Segun Ogundele</v>
       </c>
       <c r="L18" t="str">
-        <f>VLOOKUP(TRIM(D18),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D18),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M18" t="str">
@@ -4473,7 +4428,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P18" t="str">
-        <f>VLOOKUP(TRIM(D18),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L18,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q18" t="str" cm="1">
@@ -4525,7 +4480,7 @@
         <v>Dr. Oluwaseun Fashola</v>
       </c>
       <c r="L19" t="str">
-        <f>VLOOKUP(TRIM(D19),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D19),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M19" t="str">
@@ -4541,7 +4496,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P19" t="str">
-        <f>VLOOKUP(TRIM(D19),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L19,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q19" t="str" cm="1">
@@ -4593,7 +4548,7 @@
         <v>Dr. Uche Ogunleye</v>
       </c>
       <c r="L20" t="str">
-        <f>VLOOKUP(TRIM(D20),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D20),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-01</v>
       </c>
       <c r="M20" t="str">
@@ -4609,7 +4564,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P20" t="str">
-        <f>VLOOKUP(TRIM(D20),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L20,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q20" t="str" cm="1">
@@ -4661,7 +4616,7 @@
         <v>Dr. Tunde Usman</v>
       </c>
       <c r="L21" t="str">
-        <f>VLOOKUP(TRIM(D21),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D21),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-02</v>
       </c>
       <c r="M21" t="str">
@@ -4677,7 +4632,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P21" t="str">
-        <f>VLOOKUP(TRIM(D21),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L21,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q21" t="str" cm="1">
@@ -4729,7 +4684,7 @@
         <v>Dr. Adaugo Fashola</v>
       </c>
       <c r="L22" t="str">
-        <f>VLOOKUP(TRIM(D22),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D22),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M22" t="str">
@@ -4745,7 +4700,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P22" t="str">
-        <f>VLOOKUP(TRIM(D22),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L22,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q22" t="str" cm="1">
@@ -4797,7 +4752,7 @@
         <v>Dr. Ronke Nnaji</v>
       </c>
       <c r="L23" t="str">
-        <f>VLOOKUP(TRIM(D23),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D23),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M23" t="str">
@@ -4813,7 +4768,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P23" t="str">
-        <f>VLOOKUP(TRIM(D23),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L23,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q23" t="str" cm="1">
@@ -4865,7 +4820,7 @@
         <v>Dr. Adaugo Fashola</v>
       </c>
       <c r="L24" t="str">
-        <f>VLOOKUP(TRIM(D24),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D24),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M24" t="str">
@@ -4881,7 +4836,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P24" t="str">
-        <f>VLOOKUP(TRIM(D24),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L24,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q24" t="str" cm="1">
@@ -4933,7 +4888,7 @@
         <v>Dr. Damilola Abubakar</v>
       </c>
       <c r="L25" t="str">
-        <f>VLOOKUP(TRIM(D25),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D25),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M25" t="str">
@@ -4949,7 +4904,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P25" t="str">
-        <f>VLOOKUP(TRIM(D25),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L25,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q25" t="str" cm="1">
@@ -5001,7 +4956,7 @@
         <v>Dr. Tunde Usman</v>
       </c>
       <c r="L26" t="str">
-        <f>VLOOKUP(TRIM(D26),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D26),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-02</v>
       </c>
       <c r="M26" t="str">
@@ -5017,7 +4972,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P26" t="str">
-        <f>VLOOKUP(TRIM(D26),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L26,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q26" t="str" cm="1">
@@ -5069,7 +5024,7 @@
         <v>Dr. Bukola Ajayi</v>
       </c>
       <c r="L27" t="str">
-        <f>VLOOKUP(TRIM(D27),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D27),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-01</v>
       </c>
       <c r="M27" t="str">
@@ -5085,7 +5040,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P27" t="str">
-        <f>VLOOKUP(TRIM(D27),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L27,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q27" t="str" cm="1">
@@ -5137,7 +5092,7 @@
         <v>Dr. Ngozi Umar</v>
       </c>
       <c r="L28" t="str">
-        <f>VLOOKUP(TRIM(D28),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D28),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M28" t="str">
@@ -5153,7 +5108,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P28" t="str">
-        <f>VLOOKUP(TRIM(D28),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L28,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q28" t="str" cm="1">
@@ -5205,7 +5160,7 @@
         <v>Dr. Yusuf Usman</v>
       </c>
       <c r="L29" t="str">
-        <f>VLOOKUP(TRIM(D29),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D29),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M29" t="str">
@@ -5221,7 +5176,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P29" t="str">
-        <f>VLOOKUP(TRIM(D29),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L29,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q29" t="str" cm="1">
@@ -5273,7 +5228,7 @@
         <v>Dr. Zainab Lawal</v>
       </c>
       <c r="L30" t="str">
-        <f>VLOOKUP(TRIM(D30),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D30),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M30" t="str">
@@ -5289,7 +5244,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P30" t="str">
-        <f>VLOOKUP(TRIM(D30),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L30,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q30" t="str" cm="1">
@@ -5341,7 +5296,7 @@
         <v>Dr. Damilola Chidozie</v>
       </c>
       <c r="L31" t="str">
-        <f>VLOOKUP(TRIM(D31),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D31),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M31" t="str">
@@ -5357,7 +5312,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P31" t="str">
-        <f>VLOOKUP(TRIM(D31),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L31,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q31" t="str" cm="1">
@@ -5409,7 +5364,7 @@
         <v>Dr. Amaka Okafor</v>
       </c>
       <c r="L32" t="str">
-        <f>VLOOKUP(TRIM(D32),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D32),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-02</v>
       </c>
       <c r="M32" t="str">
@@ -5425,7 +5380,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P32" t="str">
-        <f>VLOOKUP(TRIM(D32),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L32,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q32" t="str" cm="1">
@@ -5477,7 +5432,7 @@
         <v>Dr. Hadiza Eze</v>
       </c>
       <c r="L33" t="str">
-        <f>VLOOKUP(TRIM(D33),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D33),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M33" t="str">
@@ -5493,7 +5448,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P33" t="str">
-        <f>VLOOKUP(TRIM(D33),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L33,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q33" t="str" cm="1">
@@ -5545,7 +5500,7 @@
         <v>Dr. Segun Ogundele</v>
       </c>
       <c r="L34" t="str">
-        <f>VLOOKUP(TRIM(D34),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D34),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-02</v>
       </c>
       <c r="M34" t="str">
@@ -5561,7 +5516,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P34" t="str">
-        <f>VLOOKUP(TRIM(D34),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L34,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q34" t="str" cm="1">
@@ -5613,7 +5568,7 @@
         <v>Dr. Oluwaseun Fashola</v>
       </c>
       <c r="L35" t="str">
-        <f>VLOOKUP(TRIM(D35),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D35),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M35" t="str">
@@ -5629,7 +5584,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P35" t="str">
-        <f>VLOOKUP(TRIM(D35),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L35,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q35" t="str" cm="1">
@@ -5681,7 +5636,7 @@
         <v>Dr. Oluwaseun Fashola</v>
       </c>
       <c r="L36" t="str">
-        <f>VLOOKUP(TRIM(D36),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D36),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M36" t="str">
@@ -5697,7 +5652,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P36" t="str">
-        <f>VLOOKUP(TRIM(D36),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L36,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q36" t="str" cm="1">
@@ -5749,7 +5704,7 @@
         <v>Dr. Maryam Eneh</v>
       </c>
       <c r="L37" t="str">
-        <f>VLOOKUP(TRIM(D37),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D37),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-03</v>
       </c>
       <c r="M37" t="str">
@@ -5765,7 +5720,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P37" t="str">
-        <f>VLOOKUP(TRIM(D37),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L37,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q37" t="str" cm="1">
@@ -5817,7 +5772,7 @@
         <v>Dr. Tunde Usman</v>
       </c>
       <c r="L38" t="str">
-        <f>VLOOKUP(TRIM(D38),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D38),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M38" t="str">
@@ -5833,7 +5788,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P38" t="str">
-        <f>VLOOKUP(TRIM(D38),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L38,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q38" t="str" cm="1">
@@ -5885,7 +5840,7 @@
         <v>Dr. Maryam Adeyemi</v>
       </c>
       <c r="L39" t="str">
-        <f>VLOOKUP(TRIM(D39),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D39),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M39" t="str">
@@ -5901,7 +5856,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P39" t="str">
-        <f>VLOOKUP(TRIM(D39),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L39,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q39" t="str" cm="1">
@@ -5953,7 +5908,7 @@
         <v>Dr. Amaka Okafor</v>
       </c>
       <c r="L40" t="str">
-        <f>VLOOKUP(TRIM(D40),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D40),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M40" t="str">
@@ -5969,7 +5924,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P40" t="str">
-        <f>VLOOKUP(TRIM(D40),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L40,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q40" t="str" cm="1">
@@ -6021,7 +5976,7 @@
         <v>Dr. Oluwaseun Ogunleye</v>
       </c>
       <c r="L41" t="str">
-        <f>VLOOKUP(TRIM(D41),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D41),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M41" t="str">
@@ -6037,7 +5992,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P41" t="str">
-        <f>VLOOKUP(TRIM(D41),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L41,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q41" t="str" cm="1">
@@ -6089,7 +6044,7 @@
         <v>Dr. Bukola Yakubu</v>
       </c>
       <c r="L42" t="str">
-        <f>VLOOKUP(TRIM(D42),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D42),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M42" t="str">
@@ -6105,7 +6060,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P42" t="str">
-        <f>VLOOKUP(TRIM(D42),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L42,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q42" t="str" cm="1">
@@ -6157,7 +6112,7 @@
         <v>Dr. Damilola Chidozie</v>
       </c>
       <c r="L43" t="str">
-        <f>VLOOKUP(TRIM(D43),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D43),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M43" t="str">
@@ -6173,7 +6128,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P43" t="str">
-        <f>VLOOKUP(TRIM(D43),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L43,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q43" t="str" cm="1">
@@ -6225,7 +6180,7 @@
         <v>Dr. Hadiza Eze</v>
       </c>
       <c r="L44" t="str">
-        <f>VLOOKUP(TRIM(D44),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D44),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M44" t="str">
@@ -6241,7 +6196,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P44" t="str">
-        <f>VLOOKUP(TRIM(D44),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L44,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q44" t="str" cm="1">
@@ -6293,7 +6248,7 @@
         <v>Dr. Adaugo Fashola</v>
       </c>
       <c r="L45" t="str">
-        <f>VLOOKUP(TRIM(D45),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D45),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-02</v>
       </c>
       <c r="M45" t="str">
@@ -6309,7 +6264,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P45" t="str">
-        <f>VLOOKUP(TRIM(D45),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L45,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q45" t="str" cm="1">
@@ -6361,7 +6316,7 @@
         <v>Dr. Adaugo Fashola</v>
       </c>
       <c r="L46" t="str">
-        <f>VLOOKUP(TRIM(D46),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D46),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M46" t="str">
@@ -6377,7 +6332,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P46" t="str">
-        <f>VLOOKUP(TRIM(D46),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L46,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q46" t="str" cm="1">
@@ -6429,7 +6384,7 @@
         <v>Dr. Maryam Adeyemi</v>
       </c>
       <c r="L47" t="str">
-        <f>VLOOKUP(TRIM(D47),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D47),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M47" t="str">
@@ -6445,7 +6400,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P47" t="str">
-        <f>VLOOKUP(TRIM(D47),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L47,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q47" t="str" cm="1">
@@ -6497,7 +6452,7 @@
         <v>Dr. Amaka Nwosu</v>
       </c>
       <c r="L48" t="str">
-        <f>VLOOKUP(TRIM(D48),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D48),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M48" t="str">
@@ -6513,7 +6468,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P48" t="str">
-        <f>VLOOKUP(TRIM(D48),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L48,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q48" t="str" cm="1">
@@ -6565,7 +6520,7 @@
         <v>Dr. Ronke Eze</v>
       </c>
       <c r="L49" t="str">
-        <f>VLOOKUP(TRIM(D49),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D49),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M49" t="str">
@@ -6581,7 +6536,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P49" t="str">
-        <f>VLOOKUP(TRIM(D49),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L49,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q49" t="str" cm="1">
@@ -6633,7 +6588,7 @@
         <v>Dr. Blessing Adekunle</v>
       </c>
       <c r="L50" t="str">
-        <f>VLOOKUP(TRIM(D50),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D50),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M50" t="str">
@@ -6649,7 +6604,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P50" t="str">
-        <f>VLOOKUP(TRIM(D50),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L50,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q50" t="str" cm="1">
@@ -6701,7 +6656,7 @@
         <v>Dr. Zainab Lawal</v>
       </c>
       <c r="L51" t="str">
-        <f>VLOOKUP(TRIM(D51),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D51),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M51" t="str">
@@ -6717,7 +6672,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P51" t="str">
-        <f>VLOOKUP(TRIM(D51),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L51,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q51" t="str" cm="1">
@@ -6769,7 +6724,7 @@
         <v>Dr. Blessing Obi</v>
       </c>
       <c r="L52" t="str">
-        <f>VLOOKUP(TRIM(D52),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D52),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-01</v>
       </c>
       <c r="M52" t="str">
@@ -6785,7 +6740,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P52" t="str">
-        <f>VLOOKUP(TRIM(D52),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L52,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q52" t="str" cm="1">
@@ -6837,7 +6792,7 @@
         <v>Dr. Ronke Nnaji</v>
       </c>
       <c r="L53" t="str">
-        <f>VLOOKUP(TRIM(D53),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D53),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M53" t="str">
@@ -6853,7 +6808,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P53" t="str">
-        <f>VLOOKUP(TRIM(D53),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L53,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q53" t="str" cm="1">
@@ -6905,7 +6860,7 @@
         <v>Dr. Bimpe Mohammed</v>
       </c>
       <c r="L54" t="str">
-        <f>VLOOKUP(TRIM(D54),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D54),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M54" t="str">
@@ -6921,7 +6876,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P54" t="str">
-        <f>VLOOKUP(TRIM(D54),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L54,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q54" t="str" cm="1">
@@ -6973,7 +6928,7 @@
         <v>Dr. Oluwaseun Fashola</v>
       </c>
       <c r="L55" t="str">
-        <f>VLOOKUP(TRIM(D55),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D55),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-03</v>
       </c>
       <c r="M55" t="str">
@@ -6989,7 +6944,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P55" t="str">
-        <f>VLOOKUP(TRIM(D55),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L55,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q55" t="str" cm="1">
@@ -7041,7 +6996,7 @@
         <v>Dr. Segun Ogundele</v>
       </c>
       <c r="L56" t="str">
-        <f>VLOOKUP(TRIM(D56),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D56),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M56" t="str">
@@ -7057,7 +7012,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P56" t="str">
-        <f>VLOOKUP(TRIM(D56),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L56,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q56" t="str" cm="1">
@@ -7109,7 +7064,7 @@
         <v>No name</v>
       </c>
       <c r="L57" t="str">
-        <f>VLOOKUP(TRIM(D57),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D57),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M57" t="str">
@@ -7125,7 +7080,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P57" t="str">
-        <f>VLOOKUP(TRIM(D57),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L57,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q57" t="str" cm="1">
@@ -7177,7 +7132,7 @@
         <v>Dr. Maryam Adeyemi</v>
       </c>
       <c r="L58" t="str">
-        <f>VLOOKUP(TRIM(D58),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D58),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M58" t="str">
@@ -7193,7 +7148,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P58" t="str">
-        <f>VLOOKUP(TRIM(D58),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L58,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q58" t="str" cm="1">
@@ -7245,7 +7200,7 @@
         <v>Dr. Maryam Adeyemi</v>
       </c>
       <c r="L59" t="str">
-        <f>VLOOKUP(TRIM(D59),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D59),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M59" t="str">
@@ -7261,7 +7216,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P59" t="str">
-        <f>VLOOKUP(TRIM(D59),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L59,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q59" t="str" cm="1">
@@ -7313,7 +7268,7 @@
         <v>Dr. Amaka Nwosu</v>
       </c>
       <c r="L60" t="str">
-        <f>VLOOKUP(TRIM(D60),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D60),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M60" t="str">
@@ -7329,7 +7284,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P60" t="str">
-        <f>VLOOKUP(TRIM(D60),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L60,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q60" t="str" cm="1">
@@ -7381,7 +7336,7 @@
         <v>No name</v>
       </c>
       <c r="L61" t="str">
-        <f>VLOOKUP(TRIM(D61),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D61),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-02</v>
       </c>
       <c r="M61" t="str">
@@ -7397,7 +7352,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P61" t="str">
-        <f>VLOOKUP(TRIM(D61),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L61,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q61" t="str" cm="1">
@@ -7449,7 +7404,7 @@
         <v>Dr. Bimpe Mohammed</v>
       </c>
       <c r="L62" t="str">
-        <f>VLOOKUP(TRIM(D62),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D62),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M62" t="str">
@@ -7465,7 +7420,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P62" t="str">
-        <f>VLOOKUP(TRIM(D62),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L62,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q62" t="str" cm="1">
@@ -7517,7 +7472,7 @@
         <v>Dr. Oluwaseun Ogunleye</v>
       </c>
       <c r="L63" t="str">
-        <f>VLOOKUP(TRIM(D63),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D63),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M63" t="str">
@@ -7533,7 +7488,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P63" t="str">
-        <f>VLOOKUP(TRIM(D63),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L63,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q63" t="str" cm="1">
@@ -7585,7 +7540,7 @@
         <v>Dr. Tunde Usman</v>
       </c>
       <c r="L64" t="str">
-        <f>VLOOKUP(TRIM(D64),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D64),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-01</v>
       </c>
       <c r="M64" t="str">
@@ -7601,7 +7556,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P64" t="str">
-        <f>VLOOKUP(TRIM(D64),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L64,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q64" t="str" cm="1">
@@ -7653,7 +7608,7 @@
         <v>Dr. Ronke Eze</v>
       </c>
       <c r="L65" t="str">
-        <f>VLOOKUP(TRIM(D65),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D65),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M65" t="str">
@@ -7669,7 +7624,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P65" t="str">
-        <f>VLOOKUP(TRIM(D65),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L65,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q65" t="str" cm="1">
@@ -7721,7 +7676,7 @@
         <v>Dr. Ronke Nnaji</v>
       </c>
       <c r="L66" t="str">
-        <f>VLOOKUP(TRIM(D66),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D66),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M66" t="str">
@@ -7737,7 +7692,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P66" t="str">
-        <f>VLOOKUP(TRIM(D66),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L66,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q66" t="str" cm="1">
@@ -7789,7 +7744,7 @@
         <v>Dr. Ronke Nnaji</v>
       </c>
       <c r="L67" t="str">
-        <f>VLOOKUP(TRIM(D67),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D67),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-03</v>
       </c>
       <c r="M67" t="str">
@@ -7805,7 +7760,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P67" t="str">
-        <f>VLOOKUP(TRIM(D67),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L67,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q67" t="str" cm="1">
@@ -7857,7 +7812,7 @@
         <v>Dr. Uche Ogunleye</v>
       </c>
       <c r="L68" t="str">
-        <f>VLOOKUP(TRIM(D68),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D68),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-01</v>
       </c>
       <c r="M68" t="str">
@@ -7873,7 +7828,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P68" t="str">
-        <f>VLOOKUP(TRIM(D68),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L68,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q68" t="str" cm="1">
@@ -7925,7 +7880,7 @@
         <v>Dr. Blessing Obi</v>
       </c>
       <c r="L69" t="str">
-        <f>VLOOKUP(TRIM(D69),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D69),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M69" t="str">
@@ -7941,7 +7896,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P69" t="str">
-        <f>VLOOKUP(TRIM(D69),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L69,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q69" t="str" cm="1">
@@ -7993,7 +7948,7 @@
         <v>Dr. Amaka Okafor</v>
       </c>
       <c r="L70" t="str">
-        <f>VLOOKUP(TRIM(D70),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D70),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-01</v>
       </c>
       <c r="M70" t="str">
@@ -8009,7 +7964,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P70" t="str">
-        <f>VLOOKUP(TRIM(D70),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L70,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q70" t="str" cm="1">
@@ -8061,7 +8016,7 @@
         <v>Dr. Maryam Adeyemi</v>
       </c>
       <c r="L71" t="str">
-        <f>VLOOKUP(TRIM(D71),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D71),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M71" t="str">
@@ -8077,7 +8032,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P71" t="str">
-        <f>VLOOKUP(TRIM(D71),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L71,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q71" t="str" cm="1">
@@ -8129,7 +8084,7 @@
         <v>Dr. Damilola Chidozie</v>
       </c>
       <c r="L72" t="str">
-        <f>VLOOKUP(TRIM(D72),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D72),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M72" t="str">
@@ -8145,7 +8100,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P72" t="str">
-        <f>VLOOKUP(TRIM(D72),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L72,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q72" t="str" cm="1">
@@ -8197,7 +8152,7 @@
         <v>Dr. Ronke Eze</v>
       </c>
       <c r="L73" t="str">
-        <f>VLOOKUP(TRIM(D73),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D73),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M73" t="str">
@@ -8213,7 +8168,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P73" t="str">
-        <f>VLOOKUP(TRIM(D73),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L73,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q73" t="str" cm="1">
@@ -8265,7 +8220,7 @@
         <v>Dr. Oluwaseun Fashola</v>
       </c>
       <c r="L74" t="str">
-        <f>VLOOKUP(TRIM(D74),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D74),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-02</v>
       </c>
       <c r="M74" t="str">
@@ -8281,7 +8236,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P74" t="str">
-        <f>VLOOKUP(TRIM(D74),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L74,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q74" t="str" cm="1">
@@ -8333,7 +8288,7 @@
         <v>Dr. Damilola Chidozie</v>
       </c>
       <c r="L75" t="str">
-        <f>VLOOKUP(TRIM(D75),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D75),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M75" t="str">
@@ -8349,7 +8304,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P75" t="str">
-        <f>VLOOKUP(TRIM(D75),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L75,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q75" t="str" cm="1">
@@ -8401,7 +8356,7 @@
         <v>Dr. Bimpe Mohammed</v>
       </c>
       <c r="L76" t="str">
-        <f>VLOOKUP(TRIM(D76),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D76),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M76" t="str">
@@ -8417,7 +8372,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P76" t="str">
-        <f>VLOOKUP(TRIM(D76),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L76,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q76" t="str" cm="1">
@@ -8469,7 +8424,7 @@
         <v>Dr. Uche Ogunleye</v>
       </c>
       <c r="L77" t="str">
-        <f>VLOOKUP(TRIM(D77),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D77),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M77" t="str">
@@ -8485,7 +8440,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P77" t="str">
-        <f>VLOOKUP(TRIM(D77),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L77,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q77" t="str" cm="1">
@@ -8537,7 +8492,7 @@
         <v>Dr. Tunde Usman</v>
       </c>
       <c r="L78" t="str">
-        <f>VLOOKUP(TRIM(D78),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D78),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M78" t="str">
@@ -8553,7 +8508,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P78" t="str">
-        <f>VLOOKUP(TRIM(D78),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L78,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q78" t="str" cm="1">
@@ -8605,7 +8560,7 @@
         <v>Dr. Oluwaseun Okoye</v>
       </c>
       <c r="L79" t="str">
-        <f>VLOOKUP(TRIM(D79),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D79),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M79" t="str">
@@ -8621,7 +8576,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P79" t="str">
-        <f>VLOOKUP(TRIM(D79),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L79,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q79" t="str" cm="1">
@@ -8673,7 +8628,7 @@
         <v>Dr. Yusuf Usman</v>
       </c>
       <c r="L80" t="str">
-        <f>VLOOKUP(TRIM(D80),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D80),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M80" t="str">
@@ -8689,7 +8644,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P80" t="str">
-        <f>VLOOKUP(TRIM(D80),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L80,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q80" t="str" cm="1">
@@ -8741,7 +8696,7 @@
         <v>Dr. Oluwaseun Okoye</v>
       </c>
       <c r="L81" t="str">
-        <f>VLOOKUP(TRIM(D81),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D81),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M81" t="str">
@@ -8757,7 +8712,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P81" t="str">
-        <f>VLOOKUP(TRIM(D81),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L81,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q81" t="str" cm="1">
@@ -8809,7 +8764,7 @@
         <v>Dr. Maryam Eneh</v>
       </c>
       <c r="L82" t="str">
-        <f>VLOOKUP(TRIM(D82),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D82),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M82" t="str">
@@ -8825,7 +8780,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P82" t="str">
-        <f>VLOOKUP(TRIM(D82),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L82,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q82" t="str" cm="1">
@@ -8877,7 +8832,7 @@
         <v>Dr. Damilola Abubakar</v>
       </c>
       <c r="L83" t="str">
-        <f>VLOOKUP(TRIM(D83),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D83),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M83" t="str">
@@ -8893,7 +8848,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P83" t="str">
-        <f>VLOOKUP(TRIM(D83),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L83,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q83" t="str" cm="1">
@@ -8945,7 +8900,7 @@
         <v>Dr. Kayode Suleiman</v>
       </c>
       <c r="L84" t="str">
-        <f>VLOOKUP(TRIM(D84),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D84),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M84" t="str">
@@ -8961,7 +8916,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P84" t="str">
-        <f>VLOOKUP(TRIM(D84),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L84,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q84" t="str" cm="1">
@@ -9013,7 +8968,7 @@
         <v>Dr. Yusuf Usman</v>
       </c>
       <c r="L85" t="str">
-        <f>VLOOKUP(TRIM(D85),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D85),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M85" t="str">
@@ -9029,7 +8984,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P85" t="str">
-        <f>VLOOKUP(TRIM(D85),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L85,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q85" t="str" cm="1">
@@ -9081,7 +9036,7 @@
         <v>Dr. Ifeoma Ibe</v>
       </c>
       <c r="L86" t="str">
-        <f>VLOOKUP(TRIM(D86),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D86),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-02</v>
       </c>
       <c r="M86" t="str">
@@ -9097,7 +9052,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P86" t="str">
-        <f>VLOOKUP(TRIM(D86),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L86,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q86" t="str" cm="1">
@@ -9149,7 +9104,7 @@
         <v>Dr. Maryam Eneh</v>
       </c>
       <c r="L87" t="str">
-        <f>VLOOKUP(TRIM(D87),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D87),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M87" t="str">
@@ -9165,7 +9120,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P87" t="str">
-        <f>VLOOKUP(TRIM(D87),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L87,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q87" t="str" cm="1">
@@ -9217,7 +9172,7 @@
         <v>Dr. Maryam Eneh</v>
       </c>
       <c r="L88" t="str">
-        <f>VLOOKUP(TRIM(D88),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D88),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M88" t="str">
@@ -9233,7 +9188,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P88" t="str">
-        <f>VLOOKUP(TRIM(D88),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L88,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q88" t="str" cm="1">
@@ -9285,7 +9240,7 @@
         <v>Dr. Amaka Nwosu</v>
       </c>
       <c r="L89" t="str">
-        <f>VLOOKUP(TRIM(D89),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D89),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M89" t="str">
@@ -9301,7 +9256,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P89" t="str">
-        <f>VLOOKUP(TRIM(D89),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L89,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q89" t="str" cm="1">
@@ -9353,7 +9308,7 @@
         <v>Dr. Ronke Eze</v>
       </c>
       <c r="L90" t="str">
-        <f>VLOOKUP(TRIM(D90),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D90),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M90" t="str">
@@ -9369,7 +9324,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P90" t="str">
-        <f>VLOOKUP(TRIM(D90),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L90,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q90" t="str" cm="1">
@@ -9421,7 +9376,7 @@
         <v>Dr. Bukola Ajayi</v>
       </c>
       <c r="L91" t="str">
-        <f>VLOOKUP(TRIM(D91),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D91),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M91" t="str">
@@ -9437,7 +9392,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P91" t="str">
-        <f>VLOOKUP(TRIM(D91),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L91,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q91" t="str" cm="1">
@@ -9489,7 +9444,7 @@
         <v>Dr. Yusuf Usman</v>
       </c>
       <c r="L92" t="str">
-        <f>VLOOKUP(TRIM(D92),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D92),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M92" t="str">
@@ -9505,7 +9460,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P92" t="str">
-        <f>VLOOKUP(TRIM(D92),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L92,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q92" t="str" cm="1">
@@ -9557,7 +9512,7 @@
         <v>Dr. Oluwaseun Okoye</v>
       </c>
       <c r="L93" t="str">
-        <f>VLOOKUP(TRIM(D93),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D93),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M93" t="str">
@@ -9573,7 +9528,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P93" t="str">
-        <f>VLOOKUP(TRIM(D93),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L93,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q93" t="str" cm="1">
@@ -9625,7 +9580,7 @@
         <v>Dr. Yusuf Usman</v>
       </c>
       <c r="L94" t="str">
-        <f>VLOOKUP(TRIM(D94),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D94),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M94" t="str">
@@ -9641,7 +9596,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P94" t="str">
-        <f>VLOOKUP(TRIM(D94),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L94,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q94" t="str" cm="1">
@@ -9693,7 +9648,7 @@
         <v>Dr. Maryam Eneh</v>
       </c>
       <c r="L95" t="str">
-        <f>VLOOKUP(TRIM(D95),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D95),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M95" t="str">
@@ -9709,7 +9664,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P95" t="str">
-        <f>VLOOKUP(TRIM(D95),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L95,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q95" t="str" cm="1">
@@ -9761,7 +9716,7 @@
         <v>Dr. Ngozi Umar</v>
       </c>
       <c r="L96" t="str">
-        <f>VLOOKUP(TRIM(D96),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D96),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M96" t="str">
@@ -9777,7 +9732,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P96" t="str">
-        <f>VLOOKUP(TRIM(D96),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L96,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q96" t="str" cm="1">
@@ -9829,7 +9784,7 @@
         <v>Dr. Segun Ibe</v>
       </c>
       <c r="L97" t="str">
-        <f>VLOOKUP(TRIM(D97),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D97),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M97" t="str">
@@ -9845,7 +9800,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P97" t="str">
-        <f>VLOOKUP(TRIM(D97),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L97,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q97" t="str" cm="1">
@@ -9897,7 +9852,7 @@
         <v>Dr. Yusuf Usman</v>
       </c>
       <c r="L98" t="str">
-        <f>VLOOKUP(TRIM(D98),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D98),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M98" t="str">
@@ -9913,7 +9868,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P98" t="str">
-        <f>VLOOKUP(TRIM(D98),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L98,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q98" t="str" cm="1">
@@ -9965,7 +9920,7 @@
         <v>Dr. Blessing Adekunle</v>
       </c>
       <c r="L99" t="str">
-        <f>VLOOKUP(TRIM(D99),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D99),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-02</v>
       </c>
       <c r="M99" t="str">
@@ -9981,7 +9936,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P99" t="str">
-        <f>VLOOKUP(TRIM(D99),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L99,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q99" t="str" cm="1">
@@ -10033,7 +9988,7 @@
         <v>Dr. Folake Bamidele</v>
       </c>
       <c r="L100" t="str">
-        <f>VLOOKUP(TRIM(D100),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D100),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M100" t="str">
@@ -10049,7 +10004,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P100" t="str">
-        <f>VLOOKUP(TRIM(D100),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L100,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q100" t="str" cm="1">
@@ -10101,7 +10056,7 @@
         <v>Dr. Bimpe Mohammed</v>
       </c>
       <c r="L101" t="str">
-        <f>VLOOKUP(TRIM(D101),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D101),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M101" t="str">
@@ -10117,7 +10072,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P101" t="str">
-        <f>VLOOKUP(TRIM(D101),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L101,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q101" t="str" cm="1">
@@ -10169,7 +10124,7 @@
         <v>Dr. Amaka Okafor</v>
       </c>
       <c r="L102" t="str">
-        <f>VLOOKUP(TRIM(D102),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D102),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M102" t="str">
@@ -10185,7 +10140,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P102" t="str">
-        <f>VLOOKUP(TRIM(D102),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L102,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q102" t="str" cm="1">
@@ -10237,7 +10192,7 @@
         <v>Dr. Segun Ibe</v>
       </c>
       <c r="L103" t="str">
-        <f>VLOOKUP(TRIM(D103),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D103),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-02</v>
       </c>
       <c r="M103" t="str">
@@ -10253,7 +10208,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P103" t="str">
-        <f>VLOOKUP(TRIM(D103),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L103,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q103" t="str" cm="1">
@@ -10305,7 +10260,7 @@
         <v>Dr. Blessing Adekunle</v>
       </c>
       <c r="L104" t="str">
-        <f>VLOOKUP(TRIM(D104),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D104),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-01</v>
       </c>
       <c r="M104" t="str">
@@ -10321,7 +10276,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P104" t="str">
-        <f>VLOOKUP(TRIM(D104),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L104,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q104" t="str" cm="1">
@@ -10373,7 +10328,7 @@
         <v>Dr. Kayode Suleiman</v>
       </c>
       <c r="L105" t="str">
-        <f>VLOOKUP(TRIM(D105),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D105),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M105" t="str">
@@ -10389,7 +10344,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P105" t="str">
-        <f>VLOOKUP(TRIM(D105),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L105,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q105" t="str" cm="1">
@@ -10441,7 +10396,7 @@
         <v>Dr. Hadiza Suleiman</v>
       </c>
       <c r="L106" t="str">
-        <f>VLOOKUP(TRIM(D106),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D106),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M106" t="str">
@@ -10457,7 +10412,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P106" t="str">
-        <f>VLOOKUP(TRIM(D106),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L106,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q106" t="str" cm="1">
@@ -10509,7 +10464,7 @@
         <v>Dr. Amaka Okafor</v>
       </c>
       <c r="L107" t="str">
-        <f>VLOOKUP(TRIM(D107),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D107),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M107" t="str">
@@ -10525,7 +10480,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P107" t="str">
-        <f>VLOOKUP(TRIM(D107),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L107,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q107" t="str" cm="1">
@@ -10577,7 +10532,7 @@
         <v>Dr. Chukwuemeka Chidozie</v>
       </c>
       <c r="L108" t="str">
-        <f>VLOOKUP(TRIM(D108),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D108),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M108" t="str">
@@ -10593,7 +10548,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P108" t="str">
-        <f>VLOOKUP(TRIM(D108),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L108,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q108" t="str" cm="1">
@@ -10645,7 +10600,7 @@
         <v>Dr. Chukwuemeka Chidozie</v>
       </c>
       <c r="L109" t="str">
-        <f>VLOOKUP(TRIM(D109),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D109),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M109" t="str">
@@ -10661,7 +10616,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P109" t="str">
-        <f>VLOOKUP(TRIM(D109),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L109,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q109" t="str" cm="1">
@@ -10713,7 +10668,7 @@
         <v>Dr. Tunde Usman</v>
       </c>
       <c r="L110" t="str">
-        <f>VLOOKUP(TRIM(D110),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D110),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M110" t="str">
@@ -10729,7 +10684,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P110" t="str">
-        <f>VLOOKUP(TRIM(D110),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L110,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q110" t="str" cm="1">
@@ -10781,7 +10736,7 @@
         <v>Dr. Chukwuemeka Chidozie</v>
       </c>
       <c r="L111" t="str">
-        <f>VLOOKUP(TRIM(D111),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D111),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M111" t="str">
@@ -10797,7 +10752,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P111" t="str">
-        <f>VLOOKUP(TRIM(D111),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L111,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q111" t="str" cm="1">
@@ -10849,7 +10804,7 @@
         <v>Dr. Ifeoma Ibe</v>
       </c>
       <c r="L112" t="str">
-        <f>VLOOKUP(TRIM(D112),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D112),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-02</v>
       </c>
       <c r="M112" t="str">
@@ -10865,7 +10820,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P112" t="str">
-        <f>VLOOKUP(TRIM(D112),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L112,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q112" t="str" cm="1">
@@ -10917,7 +10872,7 @@
         <v>Dr. Blessing Adekunle</v>
       </c>
       <c r="L113" t="str">
-        <f>VLOOKUP(TRIM(D113),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D113),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M113" t="str">
@@ -10933,7 +10888,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P113" t="str">
-        <f>VLOOKUP(TRIM(D113),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L113,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q113" t="str" cm="1">
@@ -10985,7 +10940,7 @@
         <v>Dr. Folake Bamidele</v>
       </c>
       <c r="L114" t="str">
-        <f>VLOOKUP(TRIM(D114),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D114),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M114" t="str">
@@ -11001,7 +10956,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P114" t="str">
-        <f>VLOOKUP(TRIM(D114),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L114,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q114" t="str" cm="1">
@@ -11053,7 +11008,7 @@
         <v>Dr. Oluwaseun Fashola</v>
       </c>
       <c r="L115" t="str">
-        <f>VLOOKUP(TRIM(D115),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D115),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M115" t="str">
@@ -11069,7 +11024,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P115" t="str">
-        <f>VLOOKUP(TRIM(D115),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L115,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q115" t="str" cm="1">
@@ -11121,7 +11076,7 @@
         <v>Dr. Bimpe Mohammed</v>
       </c>
       <c r="L116" t="str">
-        <f>VLOOKUP(TRIM(D116),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D116),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-01</v>
       </c>
       <c r="M116" t="str">
@@ -11137,7 +11092,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P116" t="str">
-        <f>VLOOKUP(TRIM(D116),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L116,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q116" t="str" cm="1">
@@ -11189,7 +11144,7 @@
         <v>Dr. Amaka Nwosu</v>
       </c>
       <c r="L117" t="str">
-        <f>VLOOKUP(TRIM(D117),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D117),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M117" t="str">
@@ -11205,7 +11160,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P117" t="str">
-        <f>VLOOKUP(TRIM(D117),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L117,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q117" t="str" cm="1">
@@ -11257,7 +11212,7 @@
         <v>Dr. Blessing Adekunle</v>
       </c>
       <c r="L118" t="str">
-        <f>VLOOKUP(TRIM(D118),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D118),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M118" t="str">
@@ -11273,7 +11228,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P118" t="str">
-        <f>VLOOKUP(TRIM(D118),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L118,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q118" t="str" cm="1">
@@ -11325,7 +11280,7 @@
         <v>Dr. Amaka Okafor</v>
       </c>
       <c r="L119" t="str">
-        <f>VLOOKUP(TRIM(D119),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D119),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M119" t="str">
@@ -11341,7 +11296,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P119" t="str">
-        <f>VLOOKUP(TRIM(D119),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L119,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q119" t="str" cm="1">
@@ -11393,7 +11348,7 @@
         <v>Dr. Amaka Nwosu</v>
       </c>
       <c r="L120" t="str">
-        <f>VLOOKUP(TRIM(D120),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D120),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-01</v>
       </c>
       <c r="M120" t="str">
@@ -11409,7 +11364,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P120" t="str">
-        <f>VLOOKUP(TRIM(D120),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L120,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q120" t="str" cm="1">
@@ -11461,7 +11416,7 @@
         <v>Dr. Bimpe Mohammed</v>
       </c>
       <c r="L121" t="str">
-        <f>VLOOKUP(TRIM(D121),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D121),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M121" t="str">
@@ -11477,7 +11432,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P121" t="str">
-        <f>VLOOKUP(TRIM(D121),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L121,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q121" t="str" cm="1">
@@ -11529,7 +11484,7 @@
         <v>Dr. Folake Bamidele</v>
       </c>
       <c r="L122" t="str">
-        <f>VLOOKUP(TRIM(D122),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D122),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M122" t="str">
@@ -11545,7 +11500,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P122" t="str">
-        <f>VLOOKUP(TRIM(D122),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L122,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q122" t="str" cm="1">
@@ -11597,7 +11552,7 @@
         <v>Dr. Folake Bamidele</v>
       </c>
       <c r="L123" t="str">
-        <f>VLOOKUP(TRIM(D123),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D123),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-02</v>
       </c>
       <c r="M123" t="str">
@@ -11613,7 +11568,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P123" t="str">
-        <f>VLOOKUP(TRIM(D123),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L123,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q123" t="str" cm="1">
@@ -11665,7 +11620,7 @@
         <v>Dr. Segun Ibe</v>
       </c>
       <c r="L124" t="str">
-        <f>VLOOKUP(TRIM(D124),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D124),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M124" t="str">
@@ -11681,7 +11636,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P124" t="str">
-        <f>VLOOKUP(TRIM(D124),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L124,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q124" t="str" cm="1">
@@ -11733,7 +11688,7 @@
         <v>Dr. Oluwaseun Okoye</v>
       </c>
       <c r="L125" t="str">
-        <f>VLOOKUP(TRIM(D125),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D125),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M125" t="str">
@@ -11749,7 +11704,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P125" t="str">
-        <f>VLOOKUP(TRIM(D125),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L125,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q125" t="str" cm="1">
@@ -11801,7 +11756,7 @@
         <v>Dr. Folake Bamidele</v>
       </c>
       <c r="L126" t="str">
-        <f>VLOOKUP(TRIM(D126),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D126),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-03</v>
       </c>
       <c r="M126" t="str">
@@ -11817,7 +11772,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P126" t="str">
-        <f>VLOOKUP(TRIM(D126),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L126,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q126" t="str" cm="1">
@@ -11869,7 +11824,7 @@
         <v>Dr. Ifeoma Ibe</v>
       </c>
       <c r="L127" t="str">
-        <f>VLOOKUP(TRIM(D127),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D127),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-02</v>
       </c>
       <c r="M127" t="str">
@@ -11885,7 +11840,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P127" t="str">
-        <f>VLOOKUP(TRIM(D127),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L127,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q127" t="str" cm="1">
@@ -11937,7 +11892,7 @@
         <v>Dr. Amaka Nwosu</v>
       </c>
       <c r="L128" t="str">
-        <f>VLOOKUP(TRIM(D128),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D128),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M128" t="str">
@@ -11953,7 +11908,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P128" t="str">
-        <f>VLOOKUP(TRIM(D128),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L128,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q128" t="str" cm="1">
@@ -12005,7 +11960,7 @@
         <v>Dr. Oluwaseun Ogunleye</v>
       </c>
       <c r="L129" t="str">
-        <f>VLOOKUP(TRIM(D129),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D129),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M129" t="str">
@@ -12021,7 +11976,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P129" t="str">
-        <f>VLOOKUP(TRIM(D129),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L129,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q129" t="str" cm="1">
@@ -12073,7 +12028,7 @@
         <v>Dr. Maryam Eneh</v>
       </c>
       <c r="L130" t="str">
-        <f>VLOOKUP(TRIM(D130),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D130),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M130" t="str">
@@ -12089,7 +12044,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P130" t="str">
-        <f>VLOOKUP(TRIM(D130),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L130,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q130" t="str" cm="1">
@@ -12141,7 +12096,7 @@
         <v>No name</v>
       </c>
       <c r="L131" t="str">
-        <f>VLOOKUP(TRIM(D131),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D131),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M131" t="str">
@@ -12157,7 +12112,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P131" t="str">
-        <f>VLOOKUP(TRIM(D131),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L131,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q131" t="str" cm="1">
@@ -12209,7 +12164,7 @@
         <v>Dr. Amaka Nwosu</v>
       </c>
       <c r="L132" t="str">
-        <f>VLOOKUP(TRIM(D132),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D132),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M132" t="str">
@@ -12225,7 +12180,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P132" t="str">
-        <f>VLOOKUP(TRIM(D132),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L132,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q132" t="str" cm="1">
@@ -12277,7 +12232,7 @@
         <v>Dr. Tunde Usman</v>
       </c>
       <c r="L133" t="str">
-        <f>VLOOKUP(TRIM(D133),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D133),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M133" t="str">
@@ -12293,7 +12248,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P133" t="str">
-        <f>VLOOKUP(TRIM(D133),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L133,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q133" t="str" cm="1">
@@ -12345,7 +12300,7 @@
         <v>Dr. Damilola Chidozie</v>
       </c>
       <c r="L134" t="str">
-        <f>VLOOKUP(TRIM(D134),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D134),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M134" t="str">
@@ -12361,7 +12316,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P134" t="str">
-        <f>VLOOKUP(TRIM(D134),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L134,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q134" t="str" cm="1">
@@ -12413,7 +12368,7 @@
         <v>Dr. Segun Ogundele</v>
       </c>
       <c r="L135" t="str">
-        <f>VLOOKUP(TRIM(D135),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D135),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M135" t="str">
@@ -12429,7 +12384,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P135" t="str">
-        <f>VLOOKUP(TRIM(D135),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L135,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q135" t="str" cm="1">
@@ -12481,7 +12436,7 @@
         <v>Dr. Ngozi Umar</v>
       </c>
       <c r="L136" t="str">
-        <f>VLOOKUP(TRIM(D136),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D136),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-02</v>
       </c>
       <c r="M136" t="str">
@@ -12497,7 +12452,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P136" t="str">
-        <f>VLOOKUP(TRIM(D136),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L136,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q136" t="str" cm="1">
@@ -12549,7 +12504,7 @@
         <v>Dr. Ifeoma Ibe</v>
       </c>
       <c r="L137" t="str">
-        <f>VLOOKUP(TRIM(D137),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D137),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M137" t="str">
@@ -12565,7 +12520,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P137" t="str">
-        <f>VLOOKUP(TRIM(D137),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L137,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q137" t="str" cm="1">
@@ -12617,7 +12572,7 @@
         <v>Dr. Segun Ibe</v>
       </c>
       <c r="L138" t="str">
-        <f>VLOOKUP(TRIM(D138),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D138),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M138" t="str">
@@ -12633,7 +12588,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P138" t="str">
-        <f>VLOOKUP(TRIM(D138),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L138,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q138" t="str" cm="1">
@@ -12685,7 +12640,7 @@
         <v>Dr. Bimpe Mohammed</v>
       </c>
       <c r="L139" t="str">
-        <f>VLOOKUP(TRIM(D139),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D139),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M139" t="str">
@@ -12701,7 +12656,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P139" t="str">
-        <f>VLOOKUP(TRIM(D139),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L139,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q139" t="str" cm="1">
@@ -12753,7 +12708,7 @@
         <v>Dr. Segun Ogundele</v>
       </c>
       <c r="L140" t="str">
-        <f>VLOOKUP(TRIM(D140),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D140),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-02</v>
       </c>
       <c r="M140" t="str">
@@ -12769,7 +12724,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P140" t="str">
-        <f>VLOOKUP(TRIM(D140),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L140,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q140" t="str" cm="1">
@@ -12821,7 +12776,7 @@
         <v>Dr. Tunde Usman</v>
       </c>
       <c r="L141" t="str">
-        <f>VLOOKUP(TRIM(D141),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D141),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M141" t="str">
@@ -12837,7 +12792,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P141" t="str">
-        <f>VLOOKUP(TRIM(D141),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L141,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q141" t="str" cm="1">
@@ -12889,7 +12844,7 @@
         <v>Dr. Folake Bamidele</v>
       </c>
       <c r="L142" t="str">
-        <f>VLOOKUP(TRIM(D142),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D142),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M142" t="str">
@@ -12905,7 +12860,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P142" t="str">
-        <f>VLOOKUP(TRIM(D142),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L142,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q142" t="str" cm="1">
@@ -12957,7 +12912,7 @@
         <v>Dr. Yusuf Usman</v>
       </c>
       <c r="L143" t="str">
-        <f>VLOOKUP(TRIM(D143),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D143),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-02</v>
       </c>
       <c r="M143" t="str">
@@ -12973,7 +12928,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P143" t="str">
-        <f>VLOOKUP(TRIM(D143),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L143,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q143" t="str" cm="1">
@@ -13025,7 +12980,7 @@
         <v>Dr. Hadiza Eze</v>
       </c>
       <c r="L144" t="str">
-        <f>VLOOKUP(TRIM(D144),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D144),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M144" t="str">
@@ -13041,7 +12996,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P144" t="str">
-        <f>VLOOKUP(TRIM(D144),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L144,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q144" t="str" cm="1">
@@ -13093,7 +13048,7 @@
         <v>No name</v>
       </c>
       <c r="L145" t="str">
-        <f>VLOOKUP(TRIM(D145),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D145),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M145" t="str">
@@ -13109,7 +13064,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P145" t="str">
-        <f>VLOOKUP(TRIM(D145),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L145,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q145" t="str" cm="1">
@@ -13161,7 +13116,7 @@
         <v>Dr. Damilola Chidozie</v>
       </c>
       <c r="L146" t="str">
-        <f>VLOOKUP(TRIM(D146),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D146),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M146" t="str">
@@ -13177,7 +13132,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P146" t="str">
-        <f>VLOOKUP(TRIM(D146),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L146,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q146" t="str" cm="1">
@@ -13229,7 +13184,7 @@
         <v>Dr. Blessing Adekunle</v>
       </c>
       <c r="L147" t="str">
-        <f>VLOOKUP(TRIM(D147),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D147),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M147" t="str">
@@ -13245,7 +13200,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P147" t="str">
-        <f>VLOOKUP(TRIM(D147),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L147,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q147" t="str" cm="1">
@@ -13297,7 +13252,7 @@
         <v>Dr. Ronke Nnaji</v>
       </c>
       <c r="L148" t="str">
-        <f>VLOOKUP(TRIM(D148),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D148),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M148" t="str">
@@ -13313,7 +13268,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P148" t="str">
-        <f>VLOOKUP(TRIM(D148),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L148,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q148" t="str" cm="1">
@@ -13365,7 +13320,7 @@
         <v>Dr. Oluwaseun Ogunleye</v>
       </c>
       <c r="L149" t="str">
-        <f>VLOOKUP(TRIM(D149),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D149),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M149" t="str">
@@ -13381,7 +13336,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P149" t="str">
-        <f>VLOOKUP(TRIM(D149),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L149,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q149" t="str" cm="1">
@@ -13433,7 +13388,7 @@
         <v>Dr. Segun Ogundele</v>
       </c>
       <c r="L150" t="str">
-        <f>VLOOKUP(TRIM(D150),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D150),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M150" t="str">
@@ -13449,7 +13404,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P150" t="str">
-        <f>VLOOKUP(TRIM(D150),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L150,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q150" t="str" cm="1">
@@ -13501,7 +13456,7 @@
         <v>Dr. Amaka Nwosu</v>
       </c>
       <c r="L151" t="str">
-        <f>VLOOKUP(TRIM(D151),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D151),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-02</v>
       </c>
       <c r="M151" t="str">
@@ -13517,7 +13472,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P151" t="str">
-        <f>VLOOKUP(TRIM(D151),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L151,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q151" t="str" cm="1">
@@ -13569,7 +13524,7 @@
         <v>Dr. Bukola Yakubu</v>
       </c>
       <c r="L152" t="str">
-        <f>VLOOKUP(TRIM(D152),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D152),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-01</v>
       </c>
       <c r="M152" t="str">
@@ -13585,7 +13540,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P152" t="str">
-        <f>VLOOKUP(TRIM(D152),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L152,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q152" t="str" cm="1">
@@ -13637,7 +13592,7 @@
         <v>Dr. Damilola Chidozie</v>
       </c>
       <c r="L153" t="str">
-        <f>VLOOKUP(TRIM(D153),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D153),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-01</v>
       </c>
       <c r="M153" t="str">
@@ -13653,7 +13608,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P153" t="str">
-        <f>VLOOKUP(TRIM(D153),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L153,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q153" t="str" cm="1">
@@ -13705,7 +13660,7 @@
         <v>Dr. Ngozi Umar</v>
       </c>
       <c r="L154" t="str">
-        <f>VLOOKUP(TRIM(D154),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D154),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M154" t="str">
@@ -13721,7 +13676,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P154" t="str">
-        <f>VLOOKUP(TRIM(D154),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L154,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q154" t="str" cm="1">
@@ -13773,7 +13728,7 @@
         <v>Dr. Blessing Obi</v>
       </c>
       <c r="L155" t="str">
-        <f>VLOOKUP(TRIM(D155),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D155),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-03</v>
       </c>
       <c r="M155" t="str">
@@ -13789,7 +13744,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P155" t="str">
-        <f>VLOOKUP(TRIM(D155),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L155,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q155" t="str" cm="1">
@@ -13841,7 +13796,7 @@
         <v>No name</v>
       </c>
       <c r="L156" t="str">
-        <f>VLOOKUP(TRIM(D156),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D156),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M156" t="str">
@@ -13857,7 +13812,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P156" t="str">
-        <f>VLOOKUP(TRIM(D156),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L156,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q156" t="str" cm="1">
@@ -13909,7 +13864,7 @@
         <v>Dr. Adaugo Fashola</v>
       </c>
       <c r="L157" t="str">
-        <f>VLOOKUP(TRIM(D157),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D157),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-01</v>
       </c>
       <c r="M157" t="str">
@@ -13925,7 +13880,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P157" t="str">
-        <f>VLOOKUP(TRIM(D157),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L157,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q157" t="str" cm="1">
@@ -13977,7 +13932,7 @@
         <v>Dr. Damilola Chidozie</v>
       </c>
       <c r="L158" t="str">
-        <f>VLOOKUP(TRIM(D158),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D158),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-01</v>
       </c>
       <c r="M158" t="str">
@@ -13993,7 +13948,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P158" t="str">
-        <f>VLOOKUP(TRIM(D158),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L158,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q158" t="str" cm="1">
@@ -14045,7 +14000,7 @@
         <v>Dr. Blessing Obi</v>
       </c>
       <c r="L159" t="str">
-        <f>VLOOKUP(TRIM(D159),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D159),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-03</v>
       </c>
       <c r="M159" t="str">
@@ -14061,7 +14016,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P159" t="str">
-        <f>VLOOKUP(TRIM(D159),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L159,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q159" t="str" cm="1">
@@ -14113,7 +14068,7 @@
         <v>Dr. Bukola Yakubu</v>
       </c>
       <c r="L160" t="str">
-        <f>VLOOKUP(TRIM(D160),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D160),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-01</v>
       </c>
       <c r="M160" t="str">
@@ -14129,7 +14084,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P160" t="str">
-        <f>VLOOKUP(TRIM(D160),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L160,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q160" t="str" cm="1">
@@ -14181,7 +14136,7 @@
         <v>Dr. Damilola Chidozie</v>
       </c>
       <c r="L161" t="str">
-        <f>VLOOKUP(TRIM(D161),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D161),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M161" t="str">
@@ -14197,7 +14152,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P161" t="str">
-        <f>VLOOKUP(TRIM(D161),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L161,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q161" t="str" cm="1">
@@ -14249,7 +14204,7 @@
         <v>Dr. Tunde Usman</v>
       </c>
       <c r="L162" t="str">
-        <f>VLOOKUP(TRIM(D162),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D162),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-03</v>
       </c>
       <c r="M162" t="str">
@@ -14265,7 +14220,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P162" t="str">
-        <f>VLOOKUP(TRIM(D162),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L162,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q162" t="str" cm="1">
@@ -14317,7 +14272,7 @@
         <v>Dr. Bimpe Mohammed</v>
       </c>
       <c r="L163" t="str">
-        <f>VLOOKUP(TRIM(D163),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D163),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M163" t="str">
@@ -14333,7 +14288,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P163" t="str">
-        <f>VLOOKUP(TRIM(D163),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L163,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q163" t="str" cm="1">
@@ -14385,7 +14340,7 @@
         <v>Dr. Chukwuemeka Chidozie</v>
       </c>
       <c r="L164" t="str">
-        <f>VLOOKUP(TRIM(D164),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D164),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M164" t="str">
@@ -14401,7 +14356,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P164" t="str">
-        <f>VLOOKUP(TRIM(D164),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L164,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q164" t="str" cm="1">
@@ -14453,7 +14408,7 @@
         <v>Dr. Blessing Obi</v>
       </c>
       <c r="L165" t="str">
-        <f>VLOOKUP(TRIM(D165),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D165),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M165" t="str">
@@ -14469,7 +14424,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P165" t="str">
-        <f>VLOOKUP(TRIM(D165),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L165,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q165" t="str" cm="1">
@@ -14521,7 +14476,7 @@
         <v>Dr. Damilola Abubakar</v>
       </c>
       <c r="L166" t="str">
-        <f>VLOOKUP(TRIM(D166),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D166),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-02</v>
       </c>
       <c r="M166" t="str">
@@ -14537,7 +14492,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P166" t="str">
-        <f>VLOOKUP(TRIM(D166),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L166,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q166" t="str" cm="1">
@@ -14589,7 +14544,7 @@
         <v>Dr. Maryam Eneh</v>
       </c>
       <c r="L167" t="str">
-        <f>VLOOKUP(TRIM(D167),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D167),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M167" t="str">
@@ -14605,7 +14560,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P167" t="str">
-        <f>VLOOKUP(TRIM(D167),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L167,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q167" t="str" cm="1">
@@ -14657,7 +14612,7 @@
         <v>Dr. Amaka Nwosu</v>
       </c>
       <c r="L168" t="str">
-        <f>VLOOKUP(TRIM(D168),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D168),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M168" t="str">
@@ -14673,7 +14628,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P168" t="str">
-        <f>VLOOKUP(TRIM(D168),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L168,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q168" t="str" cm="1">
@@ -14725,7 +14680,7 @@
         <v>Dr. Hadiza Eze</v>
       </c>
       <c r="L169" t="str">
-        <f>VLOOKUP(TRIM(D169),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D169),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M169" t="str">
@@ -14741,7 +14696,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P169" t="str">
-        <f>VLOOKUP(TRIM(D169),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L169,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q169" t="str" cm="1">
@@ -14793,7 +14748,7 @@
         <v>Dr. Bimpe Mohammed</v>
       </c>
       <c r="L170" t="str">
-        <f>VLOOKUP(TRIM(D170),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D170),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M170" t="str">
@@ -14809,7 +14764,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P170" t="str">
-        <f>VLOOKUP(TRIM(D170),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L170,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q170" t="str" cm="1">
@@ -14861,7 +14816,7 @@
         <v>Dr. Hadiza Suleiman</v>
       </c>
       <c r="L171" t="str">
-        <f>VLOOKUP(TRIM(D171),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D171),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M171" t="str">
@@ -14877,7 +14832,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P171" t="str">
-        <f>VLOOKUP(TRIM(D171),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L171,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q171" t="str" cm="1">
@@ -14929,7 +14884,7 @@
         <v>Dr. Bukola Yakubu</v>
       </c>
       <c r="L172" t="str">
-        <f>VLOOKUP(TRIM(D172),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D172),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M172" t="str">
@@ -14945,7 +14900,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P172" t="str">
-        <f>VLOOKUP(TRIM(D172),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L172,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q172" t="str" cm="1">
@@ -14997,7 +14952,7 @@
         <v>Dr. Tunde Usman</v>
       </c>
       <c r="L173" t="str">
-        <f>VLOOKUP(TRIM(D173),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D173),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M173" t="str">
@@ -15013,7 +14968,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P173" t="str">
-        <f>VLOOKUP(TRIM(D173),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L173,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q173" t="str" cm="1">
@@ -15065,7 +15020,7 @@
         <v>Dr. Yusuf Usman</v>
       </c>
       <c r="L174" t="str">
-        <f>VLOOKUP(TRIM(D174),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D174),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M174" t="str">
@@ -15081,7 +15036,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P174" t="str">
-        <f>VLOOKUP(TRIM(D174),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L174,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q174" t="str" cm="1">
@@ -15133,7 +15088,7 @@
         <v>Dr. Adaugo Fashola</v>
       </c>
       <c r="L175" t="str">
-        <f>VLOOKUP(TRIM(D175),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D175),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M175" t="str">
@@ -15149,7 +15104,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P175" t="str">
-        <f>VLOOKUP(TRIM(D175),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L175,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q175" t="str" cm="1">
@@ -15201,7 +15156,7 @@
         <v>Dr. Adaugo Fashola</v>
       </c>
       <c r="L176" t="str">
-        <f>VLOOKUP(TRIM(D176),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D176),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M176" t="str">
@@ -15217,7 +15172,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P176" t="str">
-        <f>VLOOKUP(TRIM(D176),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L176,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q176" t="str" cm="1">
@@ -15269,7 +15224,7 @@
         <v>Dr. Bimpe Mohammed</v>
       </c>
       <c r="L177" t="str">
-        <f>VLOOKUP(TRIM(D177),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D177),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M177" t="str">
@@ -15285,7 +15240,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P177" t="str">
-        <f>VLOOKUP(TRIM(D177),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L177,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q177" t="str" cm="1">
@@ -15337,7 +15292,7 @@
         <v>Dr. Ifeoma Ibe</v>
       </c>
       <c r="L178" t="str">
-        <f>VLOOKUP(TRIM(D178),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D178),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-02</v>
       </c>
       <c r="M178" t="str">
@@ -15353,7 +15308,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P178" t="str">
-        <f>VLOOKUP(TRIM(D178),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L178,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q178" t="str" cm="1">
@@ -15405,7 +15360,7 @@
         <v>Dr. Tunde Usman</v>
       </c>
       <c r="L179" t="str">
-        <f>VLOOKUP(TRIM(D179),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D179),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M179" t="str">
@@ -15421,7 +15376,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P179" t="str">
-        <f>VLOOKUP(TRIM(D179),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L179,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q179" t="str" cm="1">
@@ -15473,7 +15428,7 @@
         <v>Dr. Bukola Ajayi</v>
       </c>
       <c r="L180" t="str">
-        <f>VLOOKUP(TRIM(D180),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D180),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-03</v>
       </c>
       <c r="M180" t="str">
@@ -15489,7 +15444,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P180" t="str">
-        <f>VLOOKUP(TRIM(D180),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L180,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q180" t="str" cm="1">
@@ -15541,7 +15496,7 @@
         <v>Dr. Adaugo Fashola</v>
       </c>
       <c r="L181" t="str">
-        <f>VLOOKUP(TRIM(D181),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D181),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M181" t="str">
@@ -15557,7 +15512,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P181" t="str">
-        <f>VLOOKUP(TRIM(D181),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L181,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q181" t="str" cm="1">
@@ -15609,7 +15564,7 @@
         <v>Dr. Adaugo Fashola</v>
       </c>
       <c r="L182" t="str">
-        <f>VLOOKUP(TRIM(D182),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D182),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-02</v>
       </c>
       <c r="M182" t="str">
@@ -15625,7 +15580,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P182" t="str">
-        <f>VLOOKUP(TRIM(D182),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L182,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q182" t="str" cm="1">
@@ -15677,7 +15632,7 @@
         <v>Dr. Amaka Okafor</v>
       </c>
       <c r="L183" t="str">
-        <f>VLOOKUP(TRIM(D183),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D183),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M183" t="str">
@@ -15693,7 +15648,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P183" t="str">
-        <f>VLOOKUP(TRIM(D183),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L183,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q183" t="str" cm="1">
@@ -15745,7 +15700,7 @@
         <v>Dr. Ngozi Umar</v>
       </c>
       <c r="L184" t="str">
-        <f>VLOOKUP(TRIM(D184),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D184),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M184" t="str">
@@ -15761,7 +15716,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P184" t="str">
-        <f>VLOOKUP(TRIM(D184),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L184,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q184" t="str" cm="1">
@@ -15813,7 +15768,7 @@
         <v>Dr. Uche Ogunleye</v>
       </c>
       <c r="L185" t="str">
-        <f>VLOOKUP(TRIM(D185),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D185),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-03</v>
       </c>
       <c r="M185" t="str">
@@ -15829,7 +15784,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P185" t="str">
-        <f>VLOOKUP(TRIM(D185),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L185,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q185" t="str" cm="1">
@@ -15881,7 +15836,7 @@
         <v>Dr. Adaugo Fashola</v>
       </c>
       <c r="L186" t="str">
-        <f>VLOOKUP(TRIM(D186),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D186),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-03</v>
       </c>
       <c r="M186" t="str">
@@ -15897,7 +15852,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P186" t="str">
-        <f>VLOOKUP(TRIM(D186),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L186,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q186" t="str" cm="1">
@@ -15949,7 +15904,7 @@
         <v>Dr. Blessing Adekunle</v>
       </c>
       <c r="L187" t="str">
-        <f>VLOOKUP(TRIM(D187),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D187),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-01</v>
       </c>
       <c r="M187" t="str">
@@ -15965,7 +15920,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P187" t="str">
-        <f>VLOOKUP(TRIM(D187),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L187,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q187" t="str" cm="1">
@@ -16017,7 +15972,7 @@
         <v>Dr. Uche Ogunleye</v>
       </c>
       <c r="L188" t="str">
-        <f>VLOOKUP(TRIM(D188),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D188),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-PHC-02</v>
       </c>
       <c r="M188" t="str">
@@ -16033,7 +15988,7 @@
         <v>Ebiere Amadi</v>
       </c>
       <c r="P188" t="str">
-        <f>VLOOKUP(TRIM(D188),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L188,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q188" t="str" cm="1">
@@ -16085,7 +16040,7 @@
         <v>Dr. Hadiza Suleiman</v>
       </c>
       <c r="L189" t="str">
-        <f>VLOOKUP(TRIM(D189),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D189),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-02</v>
       </c>
       <c r="M189" t="str">
@@ -16101,7 +16056,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P189" t="str">
-        <f>VLOOKUP(TRIM(D189),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L189,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q189" t="str" cm="1">
@@ -16153,7 +16108,7 @@
         <v>Dr. Bukola Yakubu</v>
       </c>
       <c r="L190" t="str">
-        <f>VLOOKUP(TRIM(D190),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D190),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M190" t="str">
@@ -16169,7 +16124,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P190" t="str">
-        <f>VLOOKUP(TRIM(D190),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L190,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q190" t="str" cm="1">
@@ -16221,7 +16176,7 @@
         <v>Dr. Blessing Adekunle</v>
       </c>
       <c r="L191" t="str">
-        <f>VLOOKUP(TRIM(D191),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D191),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-02</v>
       </c>
       <c r="M191" t="str">
@@ -16237,7 +16192,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P191" t="str">
-        <f>VLOOKUP(TRIM(D191),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L191,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q191" t="str" cm="1">
@@ -16289,7 +16244,7 @@
         <v>Dr. Oluwaseun Fashola</v>
       </c>
       <c r="L192" t="str">
-        <f>VLOOKUP(TRIM(D192),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D192),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M192" t="str">
@@ -16305,7 +16260,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P192" t="str">
-        <f>VLOOKUP(TRIM(D192),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L192,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q192" t="str" cm="1">
@@ -16357,7 +16312,7 @@
         <v>Dr. Folake Bamidele</v>
       </c>
       <c r="L193" t="str">
-        <f>VLOOKUP(TRIM(D193),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D193),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-03</v>
       </c>
       <c r="M193" t="str">
@@ -16373,7 +16328,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P193" t="str">
-        <f>VLOOKUP(TRIM(D193),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L193,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q193" t="str" cm="1">
@@ -16425,7 +16380,7 @@
         <v>Dr. Damilola Chidozie</v>
       </c>
       <c r="L194" t="str">
-        <f>VLOOKUP(TRIM(D194),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D194),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M194" t="str">
@@ -16441,7 +16396,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P194" t="str">
-        <f>VLOOKUP(TRIM(D194),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L194,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q194" t="str" cm="1">
@@ -16493,7 +16448,7 @@
         <v>Dr. Maryam Eneh</v>
       </c>
       <c r="L195" t="str">
-        <f>VLOOKUP(TRIM(D195),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D195),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-03</v>
       </c>
       <c r="M195" t="str">
@@ -16509,7 +16464,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P195" t="str">
-        <f>VLOOKUP(TRIM(D195),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L195,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q195" t="str" cm="1">
@@ -16561,7 +16516,7 @@
         <v>Dr. Blessing Adekunle</v>
       </c>
       <c r="L196" t="str">
-        <f>VLOOKUP(TRIM(D196),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D196),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-LAG-02</v>
       </c>
       <c r="M196" t="str">
@@ -16577,7 +16532,7 @@
         <v>Funmilayo Adebayo</v>
       </c>
       <c r="P196" t="str">
-        <f>VLOOKUP(TRIM(D196),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L196,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q196" t="str" cm="1">
@@ -16629,7 +16584,7 @@
         <v>Dr. Oluwaseun Okoye</v>
       </c>
       <c r="L197" t="str">
-        <f>VLOOKUP(TRIM(D197),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D197),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-KAN-01</v>
       </c>
       <c r="M197" t="str">
@@ -16645,7 +16600,7 @@
         <v>Hauwa Mustapha</v>
       </c>
       <c r="P197" t="str">
-        <f>VLOOKUP(TRIM(D197),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L197,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q197" t="str" cm="1">
@@ -16697,7 +16652,7 @@
         <v>Dr. Blessing Adekunle</v>
       </c>
       <c r="L198" t="str">
-        <f>VLOOKUP(TRIM(D198),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D198),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-01</v>
       </c>
       <c r="M198" t="str">
@@ -16713,7 +16668,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P198" t="str">
-        <f>VLOOKUP(TRIM(D198),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L198,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Gold</v>
       </c>
       <c r="Q198" t="str" cm="1">
@@ -16765,7 +16720,7 @@
         <v>Dr. Hadiza Suleiman</v>
       </c>
       <c r="L199" t="str">
-        <f>VLOOKUP(TRIM(D199),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D199),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-01</v>
       </c>
       <c r="M199" t="str">
@@ -16781,7 +16736,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P199" t="str">
-        <f>VLOOKUP(TRIM(D199),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L199,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Platinum</v>
       </c>
       <c r="Q199" t="str" cm="1">
@@ -16833,7 +16788,7 @@
         <v>Dr. Tunde Usman</v>
       </c>
       <c r="L200" t="str">
-        <f>VLOOKUP(TRIM(D200),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D200),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ABJ-02</v>
       </c>
       <c r="M200" t="str">
@@ -16849,7 +16804,7 @@
         <v>Ibrahim Garba</v>
       </c>
       <c r="P200" t="str">
-        <f>VLOOKUP(TRIM(D200),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L200,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Silver</v>
       </c>
       <c r="Q200" t="str" cm="1">
@@ -16901,7 +16856,7 @@
         <v>Dr. Oluwaseun Ogunleye</v>
       </c>
       <c r="L201" t="str">
-        <f>VLOOKUP(TRIM(D201),[2]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
+        <f>VLOOKUP(TRIM(D201),[1]Hospital_Details!$A$2:$D$16,2,FALSE)</f>
         <v>MC-ENU-02</v>
       </c>
       <c r="M201" t="str">
@@ -16917,7 +16872,7 @@
         <v>Chidiebere Okoro</v>
       </c>
       <c r="P201" t="str">
-        <f>VLOOKUP(TRIM(D201),[1]Hospital_Details!A$2:D$16,4,FALSE)</f>
+        <f>VLOOKUP(L201,[2]Hospital_Details!$B$2:$D$16,3,FALSE)</f>
         <v>Bronze</v>
       </c>
       <c r="Q201" t="str" cm="1">
